--- a/batch_means_results.xlsx
+++ b/batch_means_results.xlsx
@@ -444,13 +444,13 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>126</v>
+        <v>151</v>
       </c>
       <c r="C2" t="n">
-        <v>225</v>
+        <v>250</v>
       </c>
       <c r="D2" t="n">
-        <v>0.514026615891785</v>
+        <v>0.4607989204943662</v>
       </c>
     </row>
     <row r="3">
@@ -458,13 +458,13 @@
         <v>2</v>
       </c>
       <c r="B3" t="n">
-        <v>226</v>
+        <v>251</v>
       </c>
       <c r="C3" t="n">
-        <v>325</v>
+        <v>350</v>
       </c>
       <c r="D3" t="n">
-        <v>0.4395959056701768</v>
+        <v>0.471244266613799</v>
       </c>
     </row>
     <row r="4">
@@ -472,13 +472,13 @@
         <v>3</v>
       </c>
       <c r="B4" t="n">
-        <v>326</v>
+        <v>351</v>
       </c>
       <c r="C4" t="n">
-        <v>425</v>
+        <v>450</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5166497445815973</v>
+        <v>0.4888742012201229</v>
       </c>
     </row>
     <row r="5">
@@ -486,13 +486,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="n">
-        <v>426</v>
+        <v>451</v>
       </c>
       <c r="C5" t="n">
-        <v>525</v>
+        <v>550</v>
       </c>
       <c r="D5" t="n">
-        <v>0.4561968072399718</v>
+        <v>0.4507295616133835</v>
       </c>
     </row>
     <row r="6">
@@ -500,13 +500,13 @@
         <v>5</v>
       </c>
       <c r="B6" t="n">
-        <v>526</v>
+        <v>551</v>
       </c>
       <c r="C6" t="n">
-        <v>625</v>
+        <v>650</v>
       </c>
       <c r="D6" t="n">
-        <v>0.4572994657651092</v>
+        <v>0.4607420795705219</v>
       </c>
     </row>
     <row r="7">
@@ -514,13 +514,13 @@
         <v>6</v>
       </c>
       <c r="B7" t="n">
-        <v>626</v>
+        <v>651</v>
       </c>
       <c r="C7" t="n">
-        <v>725</v>
+        <v>750</v>
       </c>
       <c r="D7" t="n">
-        <v>0.4658540407968206</v>
+        <v>0.4591784282647609</v>
       </c>
     </row>
     <row r="8">
@@ -528,13 +528,13 @@
         <v>7</v>
       </c>
       <c r="B8" t="n">
-        <v>726</v>
+        <v>751</v>
       </c>
       <c r="C8" t="n">
-        <v>825</v>
+        <v>850</v>
       </c>
       <c r="D8" t="n">
-        <v>0.4680356847940386</v>
+        <v>0.4670756783712294</v>
       </c>
     </row>
     <row r="9">
@@ -542,13 +542,13 @@
         <v>8</v>
       </c>
       <c r="B9" t="n">
-        <v>826</v>
+        <v>851</v>
       </c>
       <c r="C9" t="n">
-        <v>925</v>
+        <v>950</v>
       </c>
       <c r="D9" t="n">
-        <v>0.4243289957346101</v>
+        <v>0.4208928111352742</v>
       </c>
     </row>
     <row r="10">
@@ -556,13 +556,13 @@
         <v>9</v>
       </c>
       <c r="B10" t="n">
-        <v>926</v>
+        <v>951</v>
       </c>
       <c r="C10" t="n">
-        <v>1025</v>
+        <v>1050</v>
       </c>
       <c r="D10" t="n">
-        <v>0.4295780933585561</v>
+        <v>0.443893347030651</v>
       </c>
     </row>
     <row r="11">
@@ -570,13 +570,13 @@
         <v>10</v>
       </c>
       <c r="B11" t="n">
-        <v>1026</v>
+        <v>1051</v>
       </c>
       <c r="C11" t="n">
-        <v>1125</v>
+        <v>1150</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4559731792869077</v>
+        <v>0.449260780928133</v>
       </c>
     </row>
     <row r="12">
@@ -584,13 +584,13 @@
         <v>11</v>
       </c>
       <c r="B12" t="n">
-        <v>1126</v>
+        <v>1151</v>
       </c>
       <c r="C12" t="n">
-        <v>1225</v>
+        <v>1250</v>
       </c>
       <c r="D12" t="n">
-        <v>0.4576070369469232</v>
+        <v>0.4647207171433195</v>
       </c>
     </row>
     <row r="13">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="B13" t="n">
-        <v>1226</v>
+        <v>1251</v>
       </c>
       <c r="C13" t="n">
-        <v>1325</v>
+        <v>1350</v>
       </c>
       <c r="D13" t="n">
-        <v>0.4568547904872337</v>
+        <v>0.4565642750714397</v>
       </c>
     </row>
     <row r="14">
@@ -612,13 +612,13 @@
         <v>13</v>
       </c>
       <c r="B14" t="n">
-        <v>1326</v>
+        <v>1351</v>
       </c>
       <c r="C14" t="n">
-        <v>1425</v>
+        <v>1450</v>
       </c>
       <c r="D14" t="n">
-        <v>0.4543683264347461</v>
+        <v>0.4352261788233374</v>
       </c>
     </row>
     <row r="15">
@@ -626,13 +626,13 @@
         <v>14</v>
       </c>
       <c r="B15" t="n">
-        <v>1426</v>
+        <v>1451</v>
       </c>
       <c r="C15" t="n">
-        <v>1525</v>
+        <v>1550</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4824821038091245</v>
+        <v>0.5350511492871424</v>
       </c>
     </row>
     <row r="16">
@@ -640,13 +640,13 @@
         <v>15</v>
       </c>
       <c r="B16" t="n">
-        <v>1526</v>
+        <v>1551</v>
       </c>
       <c r="C16" t="n">
-        <v>1625</v>
+        <v>1650</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4905005574821171</v>
+        <v>0.4552643552970658</v>
       </c>
     </row>
     <row r="17">
@@ -654,13 +654,13 @@
         <v>16</v>
       </c>
       <c r="B17" t="n">
-        <v>1626</v>
+        <v>1651</v>
       </c>
       <c r="C17" t="n">
-        <v>1725</v>
+        <v>1750</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4285515454454111</v>
+        <v>0.4315012965499166</v>
       </c>
     </row>
     <row r="18">
@@ -668,13 +668,13 @@
         <v>17</v>
       </c>
       <c r="B18" t="n">
-        <v>1726</v>
+        <v>1751</v>
       </c>
       <c r="C18" t="n">
-        <v>1825</v>
+        <v>1850</v>
       </c>
       <c r="D18" t="n">
-        <v>0.4487079714435805</v>
+        <v>0.462667162113287</v>
       </c>
     </row>
     <row r="19">
@@ -682,13 +682,13 @@
         <v>18</v>
       </c>
       <c r="B19" t="n">
-        <v>1826</v>
+        <v>1851</v>
       </c>
       <c r="C19" t="n">
-        <v>1925</v>
+        <v>1950</v>
       </c>
       <c r="D19" t="n">
-        <v>0.4945554261787863</v>
+        <v>0.4691693733278712</v>
       </c>
     </row>
     <row r="20">
@@ -696,13 +696,13 @@
         <v>19</v>
       </c>
       <c r="B20" t="n">
-        <v>1926</v>
+        <v>1951</v>
       </c>
       <c r="C20" t="n">
-        <v>2025</v>
+        <v>2050</v>
       </c>
       <c r="D20" t="n">
-        <v>0.4378745166025081</v>
+        <v>0.4386299605788898</v>
       </c>
     </row>
     <row r="21">
@@ -710,13 +710,13 @@
         <v>20</v>
       </c>
       <c r="B21" t="n">
-        <v>2026</v>
+        <v>2051</v>
       </c>
       <c r="C21" t="n">
-        <v>2125</v>
+        <v>2150</v>
       </c>
       <c r="D21" t="n">
-        <v>0.4510552712060896</v>
+        <v>0.4479088036044054</v>
       </c>
     </row>
     <row r="22">
@@ -724,13 +724,13 @@
         <v>21</v>
       </c>
       <c r="B22" t="n">
-        <v>2126</v>
+        <v>2151</v>
       </c>
       <c r="C22" t="n">
-        <v>2225</v>
+        <v>2250</v>
       </c>
       <c r="D22" t="n">
-        <v>0.4483097409824366</v>
+        <v>0.4734529613529236</v>
       </c>
     </row>
     <row r="23">
@@ -738,13 +738,13 @@
         <v>22</v>
       </c>
       <c r="B23" t="n">
-        <v>2226</v>
+        <v>2251</v>
       </c>
       <c r="C23" t="n">
-        <v>2325</v>
+        <v>2350</v>
       </c>
       <c r="D23" t="n">
-        <v>0.462024646557656</v>
+        <v>0.4442308150301072</v>
       </c>
     </row>
     <row r="24">
@@ -752,13 +752,13 @@
         <v>23</v>
       </c>
       <c r="B24" t="n">
-        <v>2326</v>
+        <v>2351</v>
       </c>
       <c r="C24" t="n">
-        <v>2425</v>
+        <v>2450</v>
       </c>
       <c r="D24" t="n">
-        <v>0.4387261488747676</v>
+        <v>0.4293043761329231</v>
       </c>
     </row>
     <row r="25">
@@ -766,13 +766,13 @@
         <v>24</v>
       </c>
       <c r="B25" t="n">
-        <v>2426</v>
+        <v>2451</v>
       </c>
       <c r="C25" t="n">
-        <v>2525</v>
+        <v>2550</v>
       </c>
       <c r="D25" t="n">
-        <v>0.4166371336808579</v>
+        <v>0.4300420290262886</v>
       </c>
     </row>
     <row r="26">
@@ -780,13 +780,13 @@
         <v>25</v>
       </c>
       <c r="B26" t="n">
-        <v>2526</v>
+        <v>2551</v>
       </c>
       <c r="C26" t="n">
-        <v>2625</v>
+        <v>2650</v>
       </c>
       <c r="D26" t="n">
-        <v>0.4744582485124122</v>
+        <v>0.4827854194926928</v>
       </c>
     </row>
     <row r="27">
@@ -794,13 +794,13 @@
         <v>26</v>
       </c>
       <c r="B27" t="n">
-        <v>2626</v>
+        <v>2651</v>
       </c>
       <c r="C27" t="n">
-        <v>2725</v>
+        <v>2750</v>
       </c>
       <c r="D27" t="n">
-        <v>0.4239440392819194</v>
+        <v>0.4176455046357282</v>
       </c>
     </row>
     <row r="28">
@@ -808,13 +808,13 @@
         <v>27</v>
       </c>
       <c r="B28" t="n">
-        <v>2726</v>
+        <v>2751</v>
       </c>
       <c r="C28" t="n">
-        <v>2825</v>
+        <v>2850</v>
       </c>
       <c r="D28" t="n">
-        <v>0.4898715501035293</v>
+        <v>0.4807539420820901</v>
       </c>
     </row>
     <row r="29">
@@ -822,13 +822,13 @@
         <v>28</v>
       </c>
       <c r="B29" t="n">
-        <v>2826</v>
+        <v>2851</v>
       </c>
       <c r="C29" t="n">
-        <v>2925</v>
+        <v>2950</v>
       </c>
       <c r="D29" t="n">
-        <v>0.4217312204367452</v>
+        <v>0.4285851300296198</v>
       </c>
     </row>
     <row r="30">
@@ -836,13 +836,13 @@
         <v>29</v>
       </c>
       <c r="B30" t="n">
-        <v>2926</v>
+        <v>2951</v>
       </c>
       <c r="C30" t="n">
-        <v>3025</v>
+        <v>3050</v>
       </c>
       <c r="D30" t="n">
-        <v>0.516943381378014</v>
+        <v>0.4994095125812338</v>
       </c>
     </row>
     <row r="31">
@@ -850,13 +850,13 @@
         <v>30</v>
       </c>
       <c r="B31" t="n">
-        <v>3026</v>
+        <v>3051</v>
       </c>
       <c r="C31" t="n">
-        <v>3125</v>
+        <v>3150</v>
       </c>
       <c r="D31" t="n">
-        <v>0.4482556120455577</v>
+        <v>0.4902007969292343</v>
       </c>
     </row>
   </sheetData>
@@ -917,10 +917,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>3125</v>
+        <v>3150</v>
       </c>
       <c r="B2" t="n">
-        <v>125</v>
+        <v>150</v>
       </c>
       <c r="C2" t="n">
         <v>30</v>
@@ -929,16 +929,16 @@
         <v>100</v>
       </c>
       <c r="E2" t="n">
-        <v>0.4590332600336663</v>
+        <v>0.458193461144392</v>
       </c>
       <c r="F2" t="n">
-        <v>2.63612928289682e-05</v>
+        <v>2.204444388163266e-05</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4485323864263429</v>
+        <v>0.4485907989338891</v>
       </c>
       <c r="H2" t="n">
-        <v>0.4695341336409897</v>
+        <v>0.4677961233548948</v>
       </c>
     </row>
   </sheetData>
